--- a/docs/templates/initial-stock-survey.xlsx
+++ b/docs/templates/initial-stock-survey.xlsx
@@ -172,7 +172,10 @@
     <x:t>2. Columns are in the same order as the Add Product screen: identification → price → loose units → barcode → source → antibiotic → batch.</x:t>
   </x:si>
   <x:si>
-    <x:t>3. Required: product_name, dosage_form, unit, selling_price. generic_name is required for medicines — for bandages, tubes, masks choose dosage_form = Other and leave generic_name empty.</x:t>
+    <x:t>3. Required: product_name, manufacturer, dosage_form, unit, selling_price. generic_name is required for medicines — for bandages, tubes, masks choose dosage_form = Other and leave generic_name empty.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3b. manufacturer decides which product a row is. Two makers of the same name are two separate products, so fill it in even when the name looks unique.</x:t>
   </x:si>
   <x:si>
     <x:t>4. dosage_form and unit are dropdowns — click the cell, then the ▼. Do not type your own spelling; the import checks the value.</x:t>
@@ -286,7 +289,7 @@
     <x:t>8801234567890</x:t>
   </x:si>
   <x:si>
-    <x:t>Manufacturer</x:t>
+    <x:t>Who made it. Two makers of one name = two products</x:t>
   </x:si>
   <x:si>
     <x:t>Sanofi</x:t>
@@ -835,7 +838,7 @@
       <x:c r="L1" s="2" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="M1" s="2" t="s">
+      <x:c r="M1" s="1" t="s">
         <x:v>39</x:v>
       </x:c>
       <x:c r="N1" s="2" t="s">
@@ -23023,7 +23026,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:A14"/>
+  <x:dimension ref="A1:A15"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="130.710625" style="4" customWidth="1"/>
@@ -23091,12 +23094,17 @@
     </x:row>
     <x:row r="13" spans="1:1">
       <x:c r="A13" s="4" t="s">
+        <x:v>59</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" spans="1:1">
+      <x:c r="A14" s="4" t="s">
         <x:v>48</x:v>
       </x:c>
     </x:row>
-    <x:row r="14" spans="1:1">
-      <x:c r="A14" s="4" t="s">
-        <x:v>59</x:v>
+    <x:row r="15" spans="1:1">
+      <x:c r="A15" s="4" t="s">
+        <x:v>60</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -23124,16 +23132,16 @@
   <x:sheetData>
     <x:row r="1" spans="1:4" s="6" customFormat="1">
       <x:c r="A1" s="6" t="s">
-        <x:v>60</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B1" s="6" t="s">
-        <x:v>61</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="C1" s="6" t="s">
-        <x:v>62</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="D1" s="6" t="s">
-        <x:v>63</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:4">
@@ -23141,13 +23149,13 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="B2" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="C2" s="7" t="s">
-        <x:v>65</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="D2" s="3" t="s">
-        <x:v>66</x:v>
+        <x:v>67</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:4">
@@ -23155,13 +23163,13 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="B3" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C3" s="7" t="s">
-        <x:v>68</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="D3" s="3" t="s">
-        <x:v>69</x:v>
+        <x:v>70</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:4">
@@ -23169,13 +23177,13 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="B4" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="C4" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="D4" s="3" t="s">
-        <x:v>72</x:v>
+        <x:v>73</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:4">
@@ -23183,10 +23191,10 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="B5" s="0" t="s">
-        <x:v>73</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C5" s="7" t="s">
-        <x:v>65</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="D5" s="3" t="s">
         <x:v>1</x:v>
@@ -23197,10 +23205,10 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="B6" s="0" t="s">
-        <x:v>74</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="C6" s="7" t="s">
-        <x:v>65</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="D6" s="3" t="s">
         <x:v>1</x:v>
@@ -23211,13 +23219,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="B7" s="0" t="s">
-        <x:v>75</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="C7" s="7" t="s">
-        <x:v>65</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="D7" s="3" t="s">
-        <x:v>76</x:v>
+        <x:v>77</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:4">
@@ -23225,13 +23233,13 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="B8" s="0" t="s">
-        <x:v>77</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="C8" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="D8" s="3" t="s">
-        <x:v>78</x:v>
+        <x:v>79</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:4">
@@ -23239,13 +23247,13 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="B9" s="0" t="s">
-        <x:v>79</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="C9" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="D9" s="3" t="s">
-        <x:v>80</x:v>
+        <x:v>81</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:4">
@@ -23253,10 +23261,10 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="B10" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="C10" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="D10" s="3" t="s">
         <x:v>23</x:v>
@@ -23267,13 +23275,13 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="B11" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="C11" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="D11" s="3" t="s">
-        <x:v>84</x:v>
+        <x:v>85</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:4">
@@ -23281,13 +23289,13 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="B12" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="C12" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="D12" s="3" t="s">
-        <x:v>86</x:v>
+        <x:v>87</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:4">
@@ -23295,13 +23303,13 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="B13" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C13" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="D13" s="3" t="s">
-        <x:v>88</x:v>
+        <x:v>89</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:4">
@@ -23309,13 +23317,13 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="B14" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>90</x:v>
       </x:c>
-      <x:c r="C14" s="0" t="s">
-        <x:v>71</x:v>
+      <x:c r="C14" s="7" t="s">
+        <x:v>66</x:v>
       </x:c>
       <x:c r="D14" s="3" t="s">
-        <x:v>90</x:v>
+        <x:v>91</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:4">
@@ -23323,13 +23331,13 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="B15" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="C15" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="D15" s="3" t="s">
-        <x:v>92</x:v>
+        <x:v>93</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:4">
@@ -23337,13 +23345,13 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="B16" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="C16" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="D16" s="3" t="s">
-        <x:v>94</x:v>
+        <x:v>95</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:4">
@@ -23351,10 +23359,10 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="B17" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="C17" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="D17" s="3" t="s">
         <x:v>26</x:v>
@@ -23365,13 +23373,13 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="B18" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C18" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="D18" s="3" t="s">
-        <x:v>98</x:v>
+        <x:v>99</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:4">
@@ -23379,13 +23387,13 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="B19" s="0" t="s">
-        <x:v>99</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="C19" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="D19" s="3" t="s">
-        <x:v>100</x:v>
+        <x:v>101</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:4">
@@ -23393,13 +23401,13 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="B20" s="0" t="s">
-        <x:v>101</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="C20" s="7" t="s">
-        <x:v>102</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="D20" s="3" t="s">
-        <x:v>103</x:v>
+        <x:v>104</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:4">
@@ -23407,10 +23415,10 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="B21" s="0" t="s">
-        <x:v>104</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="C21" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="D21" s="3" t="s">
         <x:v>48</x:v>
